--- a/downloads/base_completa.xlsx
+++ b/downloads/base_completa.xlsx
@@ -3406,7 +3406,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sal de Oro</t>
+          <t>Sal de Oro II</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Construcción de una planta destinada a la producción de carbonato de litio y su infraestructura complementaria. La planta tendrá una capacidad operativa aproximada de 23.000 toneladas anuales, que se obtendrá a través de un proceso convencional de evaporación solar y tratamiento químico de salmuera.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3416,7 +3426,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Argentina S.A. (Posco)</t>
+          <t>Posco Argentina SAU SDE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>30-71922048-3</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3431,7 +3446,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Salta; Catamarca</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3440,19 +3455,54 @@
         </is>
       </c>
       <c r="L37">
-        <v>845</v>
+        <v>547</v>
+      </c>
+      <c r="M37">
+        <v>207.9364272</v>
+      </c>
+      <c r="N37">
+        <v>2335</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Aprobado</t>
         </is>
       </c>
       <c r="P37" s="2">
         <v>45595</v>
       </c>
+      <c r="Q37" s="2">
+        <v>46185</v>
+      </c>
+      <c r="R37" s="2">
+        <v>46234</v>
+      </c>
+      <c r="S37" s="2">
+        <v>46234</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Res. 1157/2026</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345279/20260731</t>
+        </is>
+      </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Globaris</t>
+          <t>Res. 1157/2026; Globaris; MECON</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Signos fuertes de preexistencia del Proyecto Sal de Oro II. POSCO Holdings aprobó la inversión de la segunda fase en octubre de 2022; en junio de 2023, antes del primer anuncio del RIGI, el Gobierno nacional y la empresa comunicaron el inicio de construcción de una planta de carbonato de litio de 23.000 toneladas anuales; y en abril de 2024 POSCO obtuvo financiamiento por hasta USD 668 millones para esa misma fase. Las coincidencias de empresa, localización, producto, capacidad y etapa indican que se trata sustancialmente del mismo proyecto incorporado posteriormente al régimen.</t>
         </is>
       </c>
     </row>
